--- a/input/images/tables/ms_refs.xlsx
+++ b/input/images/tables/ms_refs.xlsx
@@ -559,31 +559,39 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>US Core Average Blood Pressure Profile</t>
+          <t>US Core Appointment Profile</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>US Core Location Profile</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>US Core Blood Pressure Profile</t>
+          <t>US Core Average Blood Pressure Profile</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -599,11 +607,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>US Core BMI Profile</t>
+          <t>US Core Blood Pressure Profile</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -619,11 +627,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>US Core Body Height Profile</t>
+          <t>US Core BMI Profile</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -639,11 +647,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>US Core Body Temperature Profile</t>
+          <t>US Core Body Height Profile</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -659,11 +667,11 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>US Core Body Weight Profile</t>
+          <t>US Core Body Temperature Profile</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -679,11 +687,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>US Core Care Experience Preference Profile</t>
+          <t>US Core Body Weight Profile</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -699,11 +707,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>US Core CarePlan Profile</t>
+          <t>US Core Care Experience Preference Profile</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -719,11 +727,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>US Core CareTeam Profile</t>
+          <t>US Core CarePlan Profile</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -731,63 +739,63 @@
           <t>US Core Patient Profile</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>US Core PractitionerRole Profile</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>US Core RelatedPerson Profile</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>US Core Condition Encounter Diagnosis Profile</t>
+          <t>US Core CareTeam Profile</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>US Core PractitionerRole Profile</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>US Core RelatedPerson Profile</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Condition Encounter Diagnosis Profile</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
@@ -795,23 +803,19 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>US Core Coverage Profile</t>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US Core Organization Profile</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -819,19 +823,23 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>US Core Device Profile</t>
+          <t>US Core Coverage Profile</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>US Core Organization Profile</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
@@ -839,79 +847,55 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
+          <t>US Core Device Profile</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>US Core Laboratory Result Observation Profile</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>US Core DiagnosticReport Profile for Report and Note Exchange</t>
+          <t>US Core DeviceRequest Profile</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>US Core Observation Clinical Result Profile</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>US Core Organization Profile</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>US Core DocumentReference Profile</t>
+          <t>US Core DiagnosticReport Profile for Laboratory Results Reporting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -921,109 +905,133 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>US Core DiagnosticReport Profile for Report and Note Exchange</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>US Core Encounter Profile</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>US Core Condition Encounter Diagnosis Profile</t>
-        </is>
-      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>US Core Condition Problems and Health Concerns Profile</t>
+          <t>US Core Observation Clinical Result Profile</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>US Core Location Profile</t>
+          <t>US Core Organization Profile</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>US Core Organization Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>US Core FamilyMemberHistory Profile</t>
+          <t>US Core DocumentReference Profile</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>US Core Goal Profile</t>
+          <t>US Core Encounter Profile</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Condition Encounter Diagnosis Profile</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+          <t>US Core Condition Problems and Health Concerns Profile</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>US Core Location Profile</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>US Core Organization Profile</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>US Core Head Circumference Profile</t>
+          <t>US Core FamilyMemberHistory Profile</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1039,11 +1047,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>US Core Heart Rate Profile</t>
+          <t>US Core Goal Profile</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1051,7 +1059,11 @@
           <t>US Core Patient Profile</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1059,48 +1071,36 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>US Core Immunization Profile</t>
+          <t>US Core Head Circumference Profile</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>US Core Location Profile</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>US Core Location Profile</t>
+          <t>US Core Heart Rate Profile</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US Core Organization Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1111,119 +1111,111 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US Core Medication Profile</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+          <t>US Core Immunization Profile</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>US Core Location Profile</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>US Core MedicationDispense Profile</t>
+          <t>US Core Location Profile</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>US Core Medication Profile</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>US Core MedicationRequest Profile</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
+          <t>US Core Organization Profile</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>US Core MedicationRequest Profile</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
           <t>US Core Medication Profile</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>US Core Observation ADI Documentation Profile</t>
+          <t>US Core MedicationAdministration Profile</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US Core ADI DocumentReference Profile</t>
+          <t>US Core Medication Profile</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>US Core Observation Clinical Result Profile</t>
+          <t>US Core MedicationDispense Profile</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1233,25 +1225,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Medication Profile</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>US Core MedicationRequest Profile</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>US Core Laboratory Result Observation Profile</t>
+          <t>US Core MedicationRequest Profile</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1261,17 +1257,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>US Core Medication Profile</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
+          <t>US Core Patient Profile</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Practitioner Profile</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1279,11 +1275,11 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>US Core Observation Occupation Profile</t>
+          <t>US Core NutritionOrder Profile</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1291,7 +1287,11 @@
           <t>US Core Patient Profile</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
@@ -1299,56 +1299,72 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Intent Profile</t>
+          <t>US Core Observation ADI Documentation Profile</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+          <t>US Core ADI DocumentReference Profile</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US Core Observation Pregnancy Status Profile</t>
+          <t>US Core Observation Clinical Result Profile</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>US Core Observation Screening Assessment Profile</t>
+          <t>US Core Laboratory Result Observation Profile</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US Core Observation Screening Assessment Profile</t>
+          <t>US Core Encounter Profile</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1363,7 +1379,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>US Core QuestionnaireResponse Profile</t>
+          <t>US Core Specimen Profile</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1371,11 +1387,11 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>US Core Observation Sexual Orientation Profile</t>
+          <t>US Core Observation Occupation Profile</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1391,14 +1407,18 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>US Core Organization Profile</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>US Core Observation Pregnancy Intent Profile</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
@@ -1407,14 +1427,18 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>US Core Observation Pregnancy Status Profile</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
@@ -1423,71 +1447,67 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+          <t>US Core Observation Screening Assessment Profile</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>US Core Observation Screening Assessment Profile</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>US Core QuestionnaireResponse Profile</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>US Core PractitionerRole Profile</t>
+          <t>US Core Observation Sexual Orientation Profile</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Endpoint</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>US Core Location Profile</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>US Core Organization Profile</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>US Core Procedure Profile</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
+          <t>US Core Organization Profile</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
@@ -1495,23 +1515,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>US Core Provenance Profile</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Resource</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>US Core Organization Profile</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
@@ -1519,18 +1531,14 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>US Core Pulse Oximetry Profile</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
@@ -1539,43 +1547,55 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>US Core QuestionnaireResponse Profile</t>
+          <t>US Core PractitionerRole Profile</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
+          <t>Endpoint</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+          <t>US Core Location Profile</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>US Core Organization Profile</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>US Core RelatedPerson Profile</t>
+          <t>US Core Procedure Profile</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
@@ -1583,19 +1603,23 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>US Core Respiratory Rate Profile</t>
+          <t>US Core Provenance Profile</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>US Core Organization Profile</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
@@ -1603,39 +1627,31 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>US Core ServiceRequest Profile</t>
+          <t>US Core Pulse Oximetry Profile</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US Core Encounter Profile</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>US Core Simple Observation Profile</t>
+          <t>US Core QuestionnaireResponse Profile</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1655,11 +1671,11 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>US Core Smoking Status Observation Profile</t>
+          <t>US Core RelatedPerson Profile</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1667,11 +1683,7 @@
           <t>US Core Patient Profile</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>US Core Practitioner Profile</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
@@ -1679,11 +1691,11 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>US Core Specimen Profile</t>
+          <t>US Core Respiratory Rate Profile</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1699,31 +1711,39 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>US Core Treatment Intervention Preference Profile</t>
+          <t>US Core ServiceRequest Profile</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US Core Patient Profile</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>US Core Encounter Profile</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>US Core Vital Signs Profile</t>
+          <t>US Core Simple Observation Profile</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1731,12 +1751,100 @@
           <t>US Core Patient Profile</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>US Core Smoking Status Observation Profile</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>US Core Practitioner Profile</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>US Core Specimen Profile</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>54</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>US Core Treatment Intervention Preference Profile</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>55</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>US Core Vital Signs Profile</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>US Core Patient Profile</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
